--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:Z10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -656,18 +656,27 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="2" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="16" customWidth="1" min="20" max="20"/>
+    <col width="6" customWidth="1" min="21" max="21"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -751,84 +760,164 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>456</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -837,80 +926,120 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>335</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -919,80 +1048,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1001,80 +1170,120 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1083,80 +1292,120 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1165,80 +1414,120 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1247,80 +1536,120 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>216</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1329,148 +1658,212 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>20-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1107</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>599</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>473</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v/>
+      </c>
+      <c r="B10" t="n">
+        <v/>
+      </c>
+      <c r="C10" t="n">
+        <v/>
+      </c>
+      <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
+        <v/>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
         <v/>
       </c>
-      <c r="K10" t="n">
+      <c r="T10" t="n">
         <v/>
       </c>
-      <c r="L10" t="n">
+      <c r="U10" t="n">
         <v/>
       </c>
-      <c r="M10" t="n">
+      <c r="V10" t="n">
         <v/>
       </c>
-      <c r="N10" t="n">
+      <c r="W10" t="n">
         <v/>
       </c>
-      <c r="O10" t="n">
+      <c r="X10" t="n">
         <v/>
       </c>
-      <c r="P10" t="n">
+      <c r="Y10" t="n">
         <v/>
       </c>
-      <c r="Q10" t="n">
+      <c r="Z10" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -648,7 +648,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z10"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -656,27 +656,36 @@
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="2" customWidth="1" min="27" max="27"/>
+    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="16" customWidth="1" min="29" max="29"/>
+    <col width="6" customWidth="1" min="30" max="30"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -800,124 +809,204 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>456</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -926,120 +1015,160 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>335</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1048,120 +1177,160 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1170,120 +1339,160 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1292,120 +1501,160 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1414,120 +1663,160 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1536,120 +1825,160 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>216</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
+      <c r="AG8" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1658,212 +1987,292 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1107</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>599</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>473</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v/>
       </c>
-      <c r="B10" t="n">
+      <c r="K10" t="n">
         <v/>
       </c>
-      <c r="C10" t="n">
+      <c r="L10" t="n">
         <v/>
       </c>
-      <c r="D10" t="n">
+      <c r="M10" t="n">
         <v/>
       </c>
-      <c r="E10" t="n">
+      <c r="N10" t="n">
         <v/>
       </c>
-      <c r="F10" t="n">
+      <c r="O10" t="n">
         <v/>
       </c>
-      <c r="G10" t="n">
+      <c r="P10" t="n">
         <v/>
       </c>
-      <c r="H10" t="n">
+      <c r="Q10" t="n">
         <v/>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
         <v/>
       </c>
-      <c r="T10" t="n">
+      <c r="AC10" t="n">
         <v/>
       </c>
-      <c r="U10" t="n">
+      <c r="AD10" t="n">
         <v/>
       </c>
-      <c r="V10" t="n">
+      <c r="AE10" t="n">
         <v/>
       </c>
-      <c r="W10" t="n">
+      <c r="AF10" t="n">
         <v/>
       </c>
-      <c r="X10" t="n">
+      <c r="AG10" t="n">
         <v/>
       </c>
-      <c r="Y10" t="n">
+      <c r="AH10" t="n">
         <v/>
       </c>
-      <c r="Z10" t="n">
+      <c r="AI10" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -648,44 +648,53 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI10"/>
+  <dimension ref="A1:AR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="5" customWidth="1" min="16" max="16"/>
-    <col width="5" customWidth="1" min="17" max="17"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="16" max="16"/>
+    <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
-    <col width="4" customWidth="1" min="25" max="25"/>
-    <col width="4" customWidth="1" min="26" max="26"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="25" max="25"/>
+    <col width="5" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="4" customWidth="1" min="34" max="34"/>
+    <col width="4" customWidth="1" min="35" max="35"/>
+    <col width="2" customWidth="1" min="36" max="36"/>
+    <col width="15" customWidth="1" min="37" max="37"/>
+    <col width="16" customWidth="1" min="38" max="38"/>
+    <col width="6" customWidth="1" min="39" max="39"/>
+    <col width="5" customWidth="1" min="40" max="40"/>
+    <col width="5" customWidth="1" min="41" max="41"/>
+    <col width="5" customWidth="1" min="42" max="42"/>
+    <col width="5" customWidth="1" min="43" max="43"/>
+    <col width="5" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -849,164 +858,244 @@
           <t>KI</t>
         </is>
       </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>T</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>P</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>KI</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>456</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -1015,160 +1104,200 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>335</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1177,160 +1306,200 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1339,160 +1508,200 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1501,160 +1710,200 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
@@ -1663,160 +1912,200 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -1825,160 +2114,200 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>216</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -1987,292 +2316,356 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1107</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>16-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>599</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>473</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v/>
+      </c>
+      <c r="B10" t="n">
+        <v/>
+      </c>
+      <c r="C10" t="n">
+        <v/>
+      </c>
+      <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
+        <v/>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="n">
         <v/>
       </c>
-      <c r="K10" t="n">
+      <c r="T10" t="n">
         <v/>
       </c>
-      <c r="L10" t="n">
+      <c r="U10" t="n">
         <v/>
       </c>
-      <c r="M10" t="n">
+      <c r="V10" t="n">
         <v/>
       </c>
-      <c r="N10" t="n">
+      <c r="W10" t="n">
         <v/>
       </c>
-      <c r="O10" t="n">
+      <c r="X10" t="n">
         <v/>
       </c>
-      <c r="P10" t="n">
+      <c r="Y10" t="n">
         <v/>
       </c>
-      <c r="Q10" t="n">
+      <c r="Z10" t="n">
         <v/>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="n">
         <v/>
       </c>
-      <c r="AC10" t="n">
+      <c r="AL10" t="n">
         <v/>
       </c>
-      <c r="AD10" t="n">
+      <c r="AM10" t="n">
         <v/>
       </c>
-      <c r="AE10" t="n">
+      <c r="AN10" t="n">
         <v/>
       </c>
-      <c r="AF10" t="n">
+      <c r="AO10" t="n">
         <v/>
       </c>
-      <c r="AG10" t="n">
+      <c r="AP10" t="n">
         <v/>
       </c>
-      <c r="AH10" t="n">
+      <c r="AQ10" t="n">
         <v/>
       </c>
-      <c r="AI10" t="n">
+      <c r="AR10" t="n">
         <v/>
       </c>
     </row>

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -654,18 +654,18 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
@@ -674,27 +674,27 @@
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
-    <col width="5" customWidth="1" min="25" max="25"/>
-    <col width="5" customWidth="1" min="26" max="26"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="25" max="25"/>
+    <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
     <col width="6" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="4" customWidth="1" min="33" max="33"/>
-    <col width="4" customWidth="1" min="34" max="34"/>
-    <col width="4" customWidth="1" min="35" max="35"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="34" max="34"/>
+    <col width="5" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
-    <col width="5" customWidth="1" min="40" max="40"/>
+    <col width="6" customWidth="1" min="40" max="40"/>
     <col width="5" customWidth="1" min="41" max="41"/>
-    <col width="5" customWidth="1" min="42" max="42"/>
-    <col width="5" customWidth="1" min="43" max="43"/>
-    <col width="5" customWidth="1" min="44" max="44"/>
+    <col width="4" customWidth="1" min="42" max="42"/>
+    <col width="4" customWidth="1" min="43" max="43"/>
+    <col width="4" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>456</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,184 +1104,184 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>335</t>
-        </is>
-      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1306,192 +1306,192 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,192 +1710,192 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,192 +2114,192 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>720</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>141</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>720</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1107</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>17-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>16-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>599</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>473</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2516,157 +2516,189 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>23-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>22-April-2026</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>21-April-2026</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
         <v/>
       </c>
-      <c r="B10" t="n">
+      <c r="AC10" t="n">
         <v/>
       </c>
-      <c r="C10" t="n">
+      <c r="AD10" t="n">
         <v/>
       </c>
-      <c r="D10" t="n">
+      <c r="AE10" t="n">
         <v/>
       </c>
-      <c r="E10" t="n">
+      <c r="AF10" t="n">
         <v/>
       </c>
-      <c r="F10" t="n">
+      <c r="AG10" t="n">
         <v/>
       </c>
-      <c r="G10" t="n">
+      <c r="AH10" t="n">
         <v/>
       </c>
-      <c r="H10" t="n">
+      <c r="AI10" t="n">
         <v/>
       </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>17-April-2026</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="n">
-        <v/>
-      </c>
-      <c r="T10" t="n">
-        <v/>
-      </c>
-      <c r="U10" t="n">
-        <v/>
-      </c>
-      <c r="V10" t="n">
-        <v/>
-      </c>
-      <c r="W10" t="n">
-        <v/>
-      </c>
-      <c r="X10" t="n">
-        <v/>
-      </c>
-      <c r="Y10" t="n">
-        <v/>
-      </c>
-      <c r="Z10" t="n">
-        <v/>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>162</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="n">
-        <v/>
-      </c>
-      <c r="AL10" t="n">
-        <v/>
-      </c>
-      <c r="AM10" t="n">
-        <v/>
-      </c>
-      <c r="AN10" t="n">
-        <v/>
-      </c>
-      <c r="AO10" t="n">
-        <v/>
-      </c>
-      <c r="AP10" t="n">
-        <v/>
-      </c>
-      <c r="AQ10" t="n">
-        <v/>
-      </c>
-      <c r="AR10" t="n">
-        <v/>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -663,18 +663,18 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="5" customWidth="1" min="15" max="15"/>
+    <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
@@ -683,18 +683,18 @@
     <col width="6" customWidth="1" min="30" max="30"/>
     <col width="6" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
-    <col width="5" customWidth="1" min="34" max="34"/>
-    <col width="5" customWidth="1" min="35" max="35"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="4" customWidth="1" min="34" max="34"/>
+    <col width="4" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
     <col width="6" customWidth="1" min="40" max="40"/>
     <col width="5" customWidth="1" min="41" max="41"/>
-    <col width="4" customWidth="1" min="42" max="42"/>
-    <col width="4" customWidth="1" min="43" max="43"/>
-    <col width="4" customWidth="1" min="44" max="44"/>
+    <col width="5" customWidth="1" min="42" max="42"/>
+    <col width="5" customWidth="1" min="43" max="43"/>
+    <col width="5" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,167 +902,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>20-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1107</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>35</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2518,187 +2518,187 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>24-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="n">
         <v/>
       </c>
-      <c r="AC10" t="n">
+      <c r="AL10" t="n">
         <v/>
       </c>
-      <c r="AD10" t="n">
+      <c r="AM10" t="n">
         <v/>
       </c>
-      <c r="AE10" t="n">
+      <c r="AN10" t="n">
         <v/>
       </c>
-      <c r="AF10" t="n">
+      <c r="AO10" t="n">
         <v/>
       </c>
-      <c r="AG10" t="n">
+      <c r="AP10" t="n">
         <v/>
       </c>
-      <c r="AH10" t="n">
+      <c r="AQ10" t="n">
         <v/>
       </c>
-      <c r="AI10" t="n">
+      <c r="AR10" t="n">
         <v/>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>17-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -654,8 +654,8 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
@@ -672,18 +672,18 @@
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="5" customWidth="1" min="24" max="24"/>
+    <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
-    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
@@ -692,9 +692,9 @@
     <col width="6" customWidth="1" min="39" max="39"/>
     <col width="6" customWidth="1" min="40" max="40"/>
     <col width="5" customWidth="1" min="41" max="41"/>
-    <col width="5" customWidth="1" min="42" max="42"/>
-    <col width="5" customWidth="1" min="43" max="43"/>
-    <col width="5" customWidth="1" min="44" max="44"/>
+    <col width="4" customWidth="1" min="42" max="42"/>
+    <col width="4" customWidth="1" min="43" max="43"/>
+    <col width="4" customWidth="1" min="44" max="44"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -902,167 +902,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1096</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>720</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>20-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1107</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>35</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2518,187 +2518,203 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>27-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>21-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>186</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="n">
-        <v/>
-      </c>
-      <c r="AL10" t="n">
-        <v/>
-      </c>
-      <c r="AM10" t="n">
-        <v/>
-      </c>
-      <c r="AN10" t="n">
-        <v/>
-      </c>
-      <c r="AO10" t="n">
-        <v/>
-      </c>
-      <c r="AP10" t="n">
-        <v/>
-      </c>
-      <c r="AQ10" t="n">
-        <v/>
-      </c>
-      <c r="AR10" t="n">
-        <v/>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -654,8 +654,8 @@
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
     <col width="4" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
@@ -663,8 +663,8 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
@@ -681,18 +681,18 @@
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="5" customWidth="1" min="33" max="33"/>
+    <col width="4" customWidth="1" min="33" max="33"/>
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
-    <col width="6" customWidth="1" min="40" max="40"/>
+    <col width="5" customWidth="1" min="40" max="40"/>
     <col width="5" customWidth="1" min="41" max="41"/>
-    <col width="4" customWidth="1" min="42" max="42"/>
+    <col width="5" customWidth="1" min="42" max="42"/>
     <col width="4" customWidth="1" min="43" max="43"/>
     <col width="4" customWidth="1" min="44" max="44"/>
   </cols>
@@ -902,167 +902,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1141</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>1096</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>720</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2518,192 +2518,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>28-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>194</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>22-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>111</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>21-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>16</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -663,8 +663,8 @@
     <col width="15" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
     <col width="4" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
@@ -672,8 +672,8 @@
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
+    <col width="6" customWidth="1" min="23" max="23"/>
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
@@ -690,9 +690,9 @@
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
-    <col width="5" customWidth="1" min="40" max="40"/>
+    <col width="6" customWidth="1" min="40" max="40"/>
     <col width="5" customWidth="1" min="41" max="41"/>
-    <col width="5" customWidth="1" min="42" max="42"/>
+    <col width="4" customWidth="1" min="42" max="42"/>
     <col width="4" customWidth="1" min="43" max="43"/>
     <col width="4" customWidth="1" min="44" max="44"/>
   </cols>
@@ -902,167 +902,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>1096</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>211</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2518,192 +2518,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>29-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>194</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>23-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>22-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>111</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -672,8 +672,8 @@
     <col width="15" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="6" customWidth="1" min="23" max="23"/>
+    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
     <col width="4" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
@@ -681,8 +681,8 @@
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
-    <col width="6" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
+    <col width="6" customWidth="1" min="32" max="32"/>
     <col width="4" customWidth="1" min="33" max="33"/>
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
@@ -902,167 +902,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1140</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>1096</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>24-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2518,167 +2518,167 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>30-April-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>194</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>23-April-2026</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -651,7 +651,7 @@
   <dimension ref="A1:AR10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
@@ -681,8 +681,8 @@
     <col width="15" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
-    <col width="5" customWidth="1" min="31" max="31"/>
-    <col width="6" customWidth="1" min="32" max="32"/>
+    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="32" max="32"/>
     <col width="4" customWidth="1" min="33" max="33"/>
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
@@ -690,8 +690,8 @@
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
-    <col width="6" customWidth="1" min="40" max="40"/>
-    <col width="5" customWidth="1" min="41" max="41"/>
+    <col width="5" customWidth="1" min="40" max="40"/>
+    <col width="6" customWidth="1" min="41" max="41"/>
     <col width="4" customWidth="1" min="42" max="42"/>
     <col width="4" customWidth="1" min="43" max="43"/>
     <col width="4" customWidth="1" min="44" max="44"/>
@@ -902,167 +902,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>597</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1138</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>1096</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2518,192 +2518,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>01-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>194</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>27-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>194</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>24-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -654,13 +654,13 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="5" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
-    <col width="4" customWidth="1" min="6" max="6"/>
+    <col width="5" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="6" customWidth="1" min="13" max="13"/>
@@ -690,8 +690,8 @@
     <col width="15" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
-    <col width="5" customWidth="1" min="40" max="40"/>
-    <col width="6" customWidth="1" min="41" max="41"/>
+    <col width="6" customWidth="1" min="40" max="40"/>
+    <col width="5" customWidth="1" min="41" max="41"/>
     <col width="4" customWidth="1" min="42" max="42"/>
     <col width="4" customWidth="1" min="43" max="43"/>
     <col width="4" customWidth="1" min="44" max="44"/>
@@ -902,167 +902,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>721</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1138</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>1096</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2518,192 +2518,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>04-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>194</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>28-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>27-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -663,13 +663,13 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
-    <col width="6" customWidth="1" min="13" max="13"/>
+    <col width="5" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
-    <col width="4" customWidth="1" min="15" max="15"/>
+    <col width="5" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
-    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="6" customWidth="1" min="22" max="22"/>
@@ -902,167 +902,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>301</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>182</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,184 +2316,184 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>499</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>721</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1138</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1141</t>
-        </is>
-      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>0</t>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2518,184 +2518,184 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>05-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>194</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>29-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>202</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>28-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>0</t>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -672,13 +672,13 @@
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
-    <col width="6" customWidth="1" min="22" max="22"/>
+    <col width="5" customWidth="1" min="22" max="22"/>
     <col width="5" customWidth="1" min="23" max="23"/>
-    <col width="4" customWidth="1" min="24" max="24"/>
+    <col width="5" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
     <col width="2" customWidth="1" min="27" max="27"/>
-    <col width="15" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
     <col width="6" customWidth="1" min="31" max="31"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>258</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>179</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>301</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>182</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>475</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>721</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1138</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1140</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>2</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2518,192 +2518,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>06-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>30-April-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>194</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>29-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>202</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -655,7 +655,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="5" customWidth="1" min="5" max="5"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
     <col width="5" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
@@ -681,13 +681,13 @@
     <col width="13" customWidth="1" min="28" max="28"/>
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
-    <col width="6" customWidth="1" min="31" max="31"/>
+    <col width="5" customWidth="1" min="31" max="31"/>
     <col width="5" customWidth="1" min="32" max="32"/>
-    <col width="4" customWidth="1" min="33" max="33"/>
+    <col width="5" customWidth="1" min="33" max="33"/>
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
     <col width="2" customWidth="1" min="36" max="36"/>
-    <col width="15" customWidth="1" min="37" max="37"/>
+    <col width="13" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
     <col width="6" customWidth="1" min="40" max="40"/>
@@ -902,167 +902,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>271</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>258</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>179</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>301</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>182</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>1088</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>214</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>717</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>475</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>721</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1138</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1140</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2518,192 +2518,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>07-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>77</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>01-May-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>197</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>30-April-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -655,7 +655,7 @@
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
     <col width="5" customWidth="1" min="6" max="6"/>
     <col width="4" customWidth="1" min="7" max="7"/>
     <col width="4" customWidth="1" min="8" max="8"/>
@@ -664,7 +664,7 @@
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="5" customWidth="1" min="14" max="14"/>
+    <col width="6" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
@@ -690,9 +690,9 @@
     <col width="13" customWidth="1" min="37" max="37"/>
     <col width="16" customWidth="1" min="38" max="38"/>
     <col width="6" customWidth="1" min="39" max="39"/>
-    <col width="6" customWidth="1" min="40" max="40"/>
+    <col width="5" customWidth="1" min="40" max="40"/>
     <col width="5" customWidth="1" min="41" max="41"/>
-    <col width="4" customWidth="1" min="42" max="42"/>
+    <col width="5" customWidth="1" min="42" max="42"/>
     <col width="4" customWidth="1" min="43" max="43"/>
     <col width="4" customWidth="1" min="44" max="44"/>
   </cols>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>263</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>174</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>271</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>258</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>179</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>115</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>301</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>182</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>597</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>01-May-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>01-May-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>01-May-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>01-May-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>01-May-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>01-May-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>1088</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>214</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>717</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>475</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>210</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>721</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1138</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2518,192 +2518,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>08-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>88</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>04-May-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>125</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>77</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>01-May-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>197</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>5</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -657,14 +657,14 @@
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="4" customWidth="1" min="7" max="7"/>
-    <col width="4" customWidth="1" min="8" max="8"/>
+    <col width="5" customWidth="1" min="7" max="7"/>
+    <col width="5" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
     <col width="6" customWidth="1" min="12" max="12"/>
     <col width="5" customWidth="1" min="13" max="13"/>
-    <col width="6" customWidth="1" min="14" max="14"/>
+    <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
     <col width="4" customWidth="1" min="16" max="16"/>
     <col width="4" customWidth="1" min="17" max="17"/>
@@ -673,7 +673,7 @@
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="5" customWidth="1" min="23" max="23"/>
+    <col width="6" customWidth="1" min="23" max="23"/>
     <col width="5" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>253</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>263</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>174</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>271</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>166</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>258</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>179</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>301</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>182</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>11-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>215</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>716</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>1088</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>214</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>717</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>499</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>475</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>210</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>721</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2516,194 +2516,178 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v/>
+      </c>
+      <c r="B10" t="n">
+        <v/>
+      </c>
+      <c r="C10" t="n">
+        <v/>
+      </c>
+      <c r="D10" t="n">
+        <v/>
+      </c>
+      <c r="E10" t="n">
+        <v/>
+      </c>
+      <c r="F10" t="n">
+        <v/>
+      </c>
+      <c r="G10" t="n">
+        <v/>
+      </c>
+      <c r="H10" t="n">
+        <v/>
+      </c>
+      <c r="J10" t="inlineStr">
         <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>05-May-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>88</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>04-May-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>77</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -657,8 +657,8 @@
     <col width="5" customWidth="1" min="4" max="4"/>
     <col width="5" customWidth="1" min="5" max="5"/>
     <col width="5" customWidth="1" min="6" max="6"/>
-    <col width="5" customWidth="1" min="7" max="7"/>
-    <col width="5" customWidth="1" min="8" max="8"/>
+    <col width="4" customWidth="1" min="7" max="7"/>
+    <col width="4" customWidth="1" min="8" max="8"/>
     <col width="2" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
@@ -666,14 +666,14 @@
     <col width="5" customWidth="1" min="13" max="13"/>
     <col width="5" customWidth="1" min="14" max="14"/>
     <col width="5" customWidth="1" min="15" max="15"/>
-    <col width="4" customWidth="1" min="16" max="16"/>
-    <col width="4" customWidth="1" min="17" max="17"/>
+    <col width="5" customWidth="1" min="16" max="16"/>
+    <col width="5" customWidth="1" min="17" max="17"/>
     <col width="2" customWidth="1" min="18" max="18"/>
     <col width="13" customWidth="1" min="19" max="19"/>
     <col width="16" customWidth="1" min="20" max="20"/>
     <col width="6" customWidth="1" min="21" max="21"/>
     <col width="5" customWidth="1" min="22" max="22"/>
-    <col width="6" customWidth="1" min="23" max="23"/>
+    <col width="5" customWidth="1" min="23" max="23"/>
     <col width="5" customWidth="1" min="24" max="24"/>
     <col width="4" customWidth="1" min="25" max="25"/>
     <col width="4" customWidth="1" min="26" max="26"/>
@@ -682,7 +682,7 @@
     <col width="16" customWidth="1" min="29" max="29"/>
     <col width="6" customWidth="1" min="30" max="30"/>
     <col width="5" customWidth="1" min="31" max="31"/>
-    <col width="5" customWidth="1" min="32" max="32"/>
+    <col width="6" customWidth="1" min="32" max="32"/>
     <col width="5" customWidth="1" min="33" max="33"/>
     <col width="4" customWidth="1" min="34" max="34"/>
     <col width="4" customWidth="1" min="35" max="35"/>
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>253</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>184</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>263</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>174</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>271</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>161</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>166</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>258</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>179</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>497</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>168</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>477</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>06-May-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>497</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>477</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>11-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>102</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>98</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>215</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>716</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>1088</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
+      <c r="AG9" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>214</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>211</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
         <is>
           <t>717</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>499</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>168</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>475</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2516,178 +2516,178 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="n">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>12-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
         <v/>
       </c>
-      <c r="B10" t="n">
+      <c r="K10" t="n">
         <v/>
       </c>
-      <c r="C10" t="n">
+      <c r="L10" t="n">
         <v/>
       </c>
-      <c r="D10" t="n">
+      <c r="M10" t="n">
         <v/>
       </c>
-      <c r="E10" t="n">
+      <c r="N10" t="n">
         <v/>
       </c>
-      <c r="F10" t="n">
+      <c r="O10" t="n">
         <v/>
       </c>
-      <c r="G10" t="n">
+      <c r="P10" t="n">
         <v/>
       </c>
-      <c r="H10" t="n">
+      <c r="Q10" t="n">
         <v/>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>08-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>101</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>07-May-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>107</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>95</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>06-May-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>108</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>94</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>05-May-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>88</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -902,167 +902,167 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>592</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,167 +2316,167 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
@@ -2518,192 +2518,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>21-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>15-May-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>39</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
         <is>
           <t>17</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>14-May-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>25</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">

--- a/minio-report-tracker/xlxs/qaj21.xlsx
+++ b/minio-report-tracker/xlxs/qaj21.xlsx
@@ -902,192 +902,192 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>auth</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>612</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>598</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>592</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="AB2" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>598</t>
         </is>
       </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AK2" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>auth</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>612</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>597</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>auth</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>612</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>598</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1104,167 +1104,167 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>idrepo</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>414</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>idrepo</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>414</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>336</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>78</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
         <is>
           <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>idrepo</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>414</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1306,167 +1306,167 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>masterdata-ara</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="Y4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>masterdata-ara</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
         <is>
           <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>masterdata-ara</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
@@ -1508,167 +1508,167 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>masterdata-eng</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>masterdata-eng</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>944</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>masterdata-eng</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>944</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -1710,167 +1710,167 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>masterdata-fra</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="Y6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>masterdata-fra</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>945</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>929</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Y6" t="inlineStr">
+      <c r="AH6" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>masterdata-fra</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>945</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>929</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -1912,167 +1912,167 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>partner</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>509</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>350</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="K7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>partner</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>509</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>350</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>116</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
+      <c r="AG7" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AK7" t="inlineStr">
         <is>
           <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>partner</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>509</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>350</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -2114,167 +2114,167 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prereg</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="Z8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>prereg</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>288</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>282</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
+      <c r="AI8" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AK8" t="inlineStr">
         <is>
           <t>18-May-2026</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>prereg</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>288</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>282</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -2316,192 +2316,192 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>resident</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>1142</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>resident</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>1142</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>1141</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>resident</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>1142</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -2518,192 +2518,192 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>22-May-2026</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>dsl</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
           <t>21-May-2026</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>20-May-2026</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>185</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
         <is>
           <t>19-May-2026</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>175</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>24</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
+      <c r="AG10" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
         <is>
           <t>18-May-2026</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>dsl</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>201</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>15-May-2026</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>dsl</t>
-        </is>
-      </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>146</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>17</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
